--- a/G3-final-project.xlsx
+++ b/G3-final-project.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>Name</t>
   </si>
@@ -245,16 +245,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -536,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -556,7 +556,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -567,42 +567,42 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
+      <c r="A3" s="6"/>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="4"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
+      <c r="A4" s="6"/>
       <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
+      <c r="A5" s="6"/>
       <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="4"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
+      <c r="A6" s="6"/>
       <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
+      <c r="A7" s="6"/>
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -613,35 +613,35 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
+      <c r="A9" s="6"/>
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
+      <c r="A10" s="6"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
+      <c r="A11" s="6"/>
       <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
+      <c r="A12" s="6"/>
       <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -652,150 +652,143 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
+      <c r="A14" s="6"/>
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="5"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
+      <c r="A15" s="6"/>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
+      <c r="A16" s="6"/>
       <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
+      <c r="A17" s="6"/>
       <c r="B17" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
+      <c r="A18" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="B18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="A19" s="6"/>
       <c r="B19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>36</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
+      <c r="A20" s="6"/>
       <c r="B20" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
+      <c r="A21" s="6"/>
       <c r="B21" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
+      <c r="A22" s="6"/>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
+      <c r="A23" s="6"/>
       <c r="B23" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C23" s="4"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
+      <c r="A24" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="B24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="A25" s="6"/>
       <c r="B25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>38</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C25" s="5"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="3"/>
+      <c r="A26" s="6"/>
       <c r="B26" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C26" s="5"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="3"/>
+      <c r="A27" s="6"/>
       <c r="B27" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C27" s="5"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="3"/>
+      <c r="A28" s="6"/>
       <c r="B28" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C28" s="5"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
+      <c r="A29" s="6"/>
       <c r="B29" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C29" s="5"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="A24:A29"/>
     <mergeCell ref="C2:C7"/>
     <mergeCell ref="C8:C12"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="A19:A24"/>
-    <mergeCell ref="A25:A30"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="C24:C29"/>
+    <mergeCell ref="C18:C23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1"/>
     <hyperlink ref="C8" r:id="rId2"/>
     <hyperlink ref="C13" r:id="rId3"/>
-    <hyperlink ref="C19" r:id="rId4"/>
+    <hyperlink ref="C18" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
@@ -816,7 +809,7 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>39</v>
       </c>
     </row>

--- a/G3-final-project.xlsx
+++ b/G3-final-project.xlsx
@@ -246,14 +246,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -556,233 +556,233 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
+      <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="5"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="5"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="5"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="5"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
+      <c r="A10" s="4"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
+      <c r="A11" s="4"/>
       <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
+      <c r="A12" s="4"/>
       <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
+      <c r="A14" s="4"/>
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5"/>
+      <c r="C14" s="6"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
+      <c r="A15" s="4"/>
       <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="6"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
+      <c r="A16" s="4"/>
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="5"/>
+      <c r="C16" s="6"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
+      <c r="A17" s="4"/>
       <c r="B17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="5"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
+      <c r="A19" s="4"/>
       <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="4"/>
+      <c r="C19" s="5"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
+      <c r="A20" s="4"/>
       <c r="B20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="4"/>
+      <c r="C20" s="5"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
+      <c r="A21" s="4"/>
       <c r="B21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="5"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
+      <c r="A22" s="4"/>
       <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="5"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
+      <c r="A23" s="4"/>
       <c r="B23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="5"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
+      <c r="A25" s="4"/>
       <c r="B25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="5"/>
+      <c r="C25" s="6"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
+      <c r="A26" s="4"/>
       <c r="B26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="5"/>
+      <c r="C26" s="6"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
+      <c r="A27" s="4"/>
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5"/>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
+      <c r="A28" s="4"/>
       <c r="B28" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="5"/>
+      <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
+      <c r="A29" s="4"/>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="5"/>
+      <c r="C29" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C2:C7"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="C24:C29"/>
+    <mergeCell ref="C18:C23"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="A13:A17"/>
     <mergeCell ref="A18:A23"/>
     <mergeCell ref="A24:A29"/>
-    <mergeCell ref="C2:C7"/>
-    <mergeCell ref="C8:C12"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="C24:C29"/>
-    <mergeCell ref="C18:C23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1"/>

--- a/G3-final-project.xlsx
+++ b/G3-final-project.xlsx
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
-  <si>
-    <t>Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>Group Number</t>
   </si>
@@ -150,20 +147,35 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Deadline ==&gt; 31/7 - 6:PM</t>
-  </si>
-  <si>
-    <t>Discussion ==&gt; 1/8</t>
-  </si>
-  <si>
     <t>Excel sheet ==&gt; github project link , Group Number , Group Memebers Name , linkedin link</t>
+  </si>
+  <si>
+    <t>Members Name</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>VisioCreate Template</t>
+  </si>
+  <si>
+    <t>Shopery Template</t>
+  </si>
+  <si>
+    <t>Clicon Template</t>
+  </si>
+  <si>
+    <t>Discussion ==&gt; 1/8 - 10:00 AM</t>
+  </si>
+  <si>
+    <t>Deadline ==&gt; 31/7 - 6:00 PM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,6 +194,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -241,11 +260,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -536,243 +561,285 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="171.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="C2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="6"/>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C8" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="1" t="s">
+      <c r="D8" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="6"/>
+      <c r="B21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="6"/>
+      <c r="B23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6"/>
+      <c r="B25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="6"/>
+      <c r="B28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="6"/>
+      <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="5"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="5"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="5"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="6"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="6"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="6"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="5"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="5"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="5"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="5"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="6"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="4"/>
-      <c r="B26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="6"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
-      <c r="B27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
-      <c r="B28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="6"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
-      <c r="B29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="6"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="15">
     <mergeCell ref="C2:C7"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="C13:C17"/>
@@ -783,6 +850,11 @@
     <mergeCell ref="A13:A17"/>
     <mergeCell ref="A18:A23"/>
     <mergeCell ref="A24:A29"/>
+    <mergeCell ref="D2:D7"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="D18:D23"/>
+    <mergeCell ref="D24:D29"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1"/>
@@ -805,27 +877,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/G3-final-project.xlsx
+++ b/G3-final-project.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -268,17 +268,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -585,276 +585,276 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
+      <c r="A3" s="7"/>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="8"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
+      <c r="A4" s="7"/>
       <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
+      <c r="A5" s="7"/>
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="8"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
+      <c r="A6" s="7"/>
       <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="8"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
+      <c r="A7" s="7"/>
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>31</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
+      <c r="A9" s="7"/>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="8"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
+      <c r="A10" s="7"/>
       <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="8"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
+      <c r="A11" s="7"/>
       <c r="B11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="8"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
+      <c r="A12" s="7"/>
       <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="8"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="8" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
+      <c r="A14" s="7"/>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
+      <c r="A15" s="7"/>
       <c r="B15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="8"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
+      <c r="A16" s="7"/>
       <c r="B16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="8"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
+      <c r="A17" s="7"/>
       <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="8"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
+      <c r="A19" s="7"/>
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="8"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
+      <c r="A20" s="7"/>
       <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="8"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
+      <c r="A21" s="7"/>
       <c r="B21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="8"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
+      <c r="A22" s="7"/>
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
+      <c r="A23" s="7"/>
       <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="8"/>
     </row>
     <row r="24" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="8" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
+      <c r="A25" s="7"/>
       <c r="B25" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="8"/>
     </row>
     <row r="26" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
+      <c r="A26" s="7"/>
       <c r="B26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="8"/>
     </row>
     <row r="27" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
+      <c r="A27" s="7"/>
       <c r="B27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
+      <c r="A28" s="7"/>
       <c r="B28" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="8"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
+      <c r="A29" s="7"/>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="D2:D7"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="D18:D23"/>
+    <mergeCell ref="D24:D29"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="A24:A29"/>
     <mergeCell ref="C2:C7"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="C13:C17"/>
     <mergeCell ref="C24:C29"/>
     <mergeCell ref="C18:C23"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A23"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="D2:D7"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="D13:D17"/>
-    <mergeCell ref="D18:D23"/>
-    <mergeCell ref="D24:D29"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1"/>
